--- a/三合一單自動產生器/地點代號對照表.xlsx
+++ b/三合一單自動產生器/地點代號對照表.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" concurrentManualCount="8"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,10 +39,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>18P3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EF180183B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -56,6 +52,10 @@
   </si>
   <si>
     <t>12P7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18P3B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -389,12 +389,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14.375" customWidth="1"/>
+    <col min="1" max="2" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -402,15 +402,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -418,20 +418,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/三合一單自動產生器/地點代號對照表.xlsx
+++ b/三合一單自動產生器/地點代號對照表.xlsx
@@ -39,10 +39,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>18P3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EF180183B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -56,6 +52,10 @@
   </si>
   <si>
     <t>12P7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18P3B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -407,7 +407,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -420,18 +420,18 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/三合一單自動產生器/地點代號對照表.xlsx
+++ b/三合一單自動產生器/地點代號對照表.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" concurrentManualCount="8"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>短地點</t>
   </si>
@@ -35,10 +35,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>E1550156A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EF180183B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -47,15 +43,26 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>E1550155A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>12P7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>18P3B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1550L156</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1550L155</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EF150L154</t>
+  </si>
+  <si>
+    <t>15P4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -63,7 +70,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,6 +88,12 @@
     <font>
       <b/>
       <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -105,9 +118,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -388,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14.42578125" customWidth="1"/>
@@ -407,7 +421,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -415,23 +429,31 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/三合一單自動產生器/地點代號對照表.xlsx
+++ b/三合一單自動產生器/地點代號對照表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>E01500002</t>
+          <t>EF150L152</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>E01500003</t>
+          <t>EF150L153</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>E1550155A</t>
+          <t>E1550L155</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>E1550156A</t>
+          <t>E1550L156</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>E01500007</t>
+          <t>E1550L157</t>
         </is>
       </c>
     </row>
@@ -785,6 +785,18 @@
       <c r="B31" t="inlineStr">
         <is>
           <t>EB300005A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>18P3A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EF180183A</t>
         </is>
       </c>
     </row>
